--- a/data/trans_dic/P64D$noloshace_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P64D$noloshace_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios</t>
+          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,76</t>
+          <t>0,0; 11,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,11</t>
+          <t>1,06; 6,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,37</t>
+          <t>0,82; 8,52</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,0; 4,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 3,19</t>
+          <t>0,19; 3,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,27</t>
+          <t>0,32; 2,9</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,0; 5,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,95</t>
+          <t>0,47; 4,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,46</t>
+          <t>0,48; 3,41</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 16,9</t>
+          <t>5,26; 17,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,3</t>
+          <t>0,65; 4,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,12</t>
+          <t>2,61; 8,22</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 7,85</t>
+          <t>0,14; 6,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,96</t>
+          <t>0,87; 5,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,9</t>
+          <t>0,89; 5,12</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,03; 10,01</t>
+          <t>4,13; 10,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,63</t>
+          <t>4,02; 9,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,73; 8,81</t>
+          <t>4,86; 8,93</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,87; 6,76</t>
+          <t>1,0; 6,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,34; 9,38</t>
+          <t>4,22; 9,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,81</t>
+          <t>1,9; 6,64</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,97</t>
+          <t>2,47; 5,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,53</t>
+          <t>2,74; 4,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,44</t>
+          <t>2,78; 4,44</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios</t>
+          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 20684</t>
+          <t>0; 22661</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1605; 8820</t>
+          <t>1535; 9026</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2705; 28168</t>
+          <t>2753; 28677</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 10538</t>
+          <t>0; 11534</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>164; 5286</t>
+          <t>318; 5036</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1671; 13465</t>
+          <t>1327; 11932</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6980</t>
+          <t>0; 7583</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>570; 4768</t>
+          <t>572; 5236</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1218; 9338</t>
+          <t>1300; 9192</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8391; 28292</t>
+          <t>8806; 28884</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2195; 11126</t>
+          <t>1685; 11412</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10486; 34605</t>
+          <t>11122; 35051</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>320; 8967</t>
+          <t>164; 7073</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>895; 6388</t>
+          <t>928; 5928</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2175; 10840</t>
+          <t>1963; 11324</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1661</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1274</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1491</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13466; 33459</t>
+          <t>13801; 34549</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12826; 29547</t>
+          <t>12323; 30623</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30313; 56438</t>
+          <t>31156; 57267</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5455; 42444</t>
+          <t>6304; 41395</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11754; 25423</t>
+          <t>11439; 25360</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>18682; 61223</t>
+          <t>17076; 59690</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>48000; 97633</t>
+          <t>48465; 99132</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>38912; 66157</t>
+          <t>40003; 66794</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>96243; 151993</t>
+          <t>95297; 152098</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$noloshace_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P64D$noloshace_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,79</t>
+          <t>0,0; 6,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,25</t>
+          <t>0,92; 4,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 8,52</t>
+          <t>0,7; 4,68</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 4,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,04</t>
+          <t>0,41; 3,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,9</t>
+          <t>0,44; 3,15</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>1,49%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,1</t>
+          <t>0,0; 4,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,33</t>
+          <t>0,48; 4,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,41</t>
+          <t>0,47; 3,45</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 17,26</t>
+          <t>4,57; 14,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,41</t>
+          <t>1,86; 6,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 8,22</t>
+          <t>3,89; 10,28</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 6,19</t>
+          <t>0,55; 7,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,53</t>
+          <t>0,72; 4,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,12</t>
+          <t>1,06; 4,95</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,13; 10,34</t>
+          <t>5,13; 11,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,02; 9,98</t>
+          <t>4,78; 10,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,86; 8,93</t>
+          <t>5,82; 9,73</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,59</t>
+          <t>3,73; 8,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,22; 9,35</t>
+          <t>4,77; 9,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,64</t>
+          <t>4,55; 8,05</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,04</t>
+          <t>3,48; 5,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,57</t>
+          <t>3,27; 5,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,44</t>
+          <t>3,67; 5,15</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>6298</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 22661</t>
+          <t>0; 13504</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1535; 9026</t>
+          <t>1402; 7384</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2753; 28677</t>
+          <t>2456; 16549</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>5437</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 11534</t>
+          <t>0; 12198</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>318; 5036</t>
+          <t>704; 6008</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1327; 11932</t>
+          <t>1874; 13487</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4055</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7583</t>
+          <t>0; 7007</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>572; 5236</t>
+          <t>588; 5785</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1300; 9192</t>
+          <t>1274; 9405</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>16158</t>
+          <t>17863</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21780</t>
+          <t>24423</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8806; 28884</t>
+          <t>9598; 30471</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1685; 11412</t>
+          <t>3362; 11546</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11122; 35051</t>
+          <t>15195; 40198</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>6161</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>164; 7073</t>
+          <t>750; 10258</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>928; 5928</t>
+          <t>865; 5847</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1963; 11324</t>
+          <t>2698; 12658</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>22320</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>19523</t>
+          <t>25022</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>41843</t>
+          <t>55670</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13801; 34549</t>
+          <t>19863; 43718</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12323; 30623</t>
+          <t>17290; 37439</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31156; 57267</t>
+          <t>43576; 72903</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>22515</t>
+          <t>25816</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>17115</t>
+          <t>20992</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39630</t>
+          <t>46808</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6304; 41395</t>
+          <t>16984; 38133</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11439; 25360</t>
+          <t>14887; 30585</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17076; 59690</t>
+          <t>34882; 61739</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>73386</t>
+          <t>86023</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>52237</t>
+          <t>62829</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>125623</t>
+          <t>148852</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>48465; 99132</t>
+          <t>67045; 108552</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>40003; 66794</t>
+          <t>49386; 77749</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>95297; 152098</t>
+          <t>126351; 177170</t>
         </is>
       </c>
     </row>
